--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.067961</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H2" t="n">
         <v>154</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35720</v>
+        <v>35722</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -590,10 +590,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>257</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.519747</v>
+        <v>4.5178437</v>
       </c>
       <c r="G3" t="n">
-        <v>30140</v>
+        <v>30146</v>
       </c>
       <c r="H3" t="n">
-        <v>8878</v>
+        <v>8880</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2334702</v>
+        <v>2336054</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3121</v>
+        <v>3137</v>
       </c>
       <c r="O3" t="n">
         <v>279</v>
@@ -662,10 +662,10 @@
         <v>313</v>
       </c>
       <c r="Q3" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="R3" t="n">
-        <v>25906</v>
+        <v>25897</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5178437</v>
+        <v>4.5182023</v>
       </c>
       <c r="G3" t="n">
-        <v>30146</v>
+        <v>30147</v>
       </c>
       <c r="H3" t="n">
-        <v>8880</v>
+        <v>8884</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3137</v>
+        <v>3134</v>
       </c>
       <c r="O3" t="n">
         <v>279</v>
@@ -665,7 +665,7 @@
         <v>514</v>
       </c>
       <c r="R3" t="n">
-        <v>25897</v>
+        <v>25902</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>4.009901</v>
       </c>
       <c r="G2" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35722</v>
+        <v>35818</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -590,10 +590,10 @@
         <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5182023</v>
+        <v>4.5201044</v>
       </c>
       <c r="G3" t="n">
-        <v>30147</v>
+        <v>30161</v>
       </c>
       <c r="H3" t="n">
         <v>8884</v>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2336054</v>
+        <v>2337395</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.40.1</t>
+          <t>4.41.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="O3" t="n">
         <v>279</v>
       </c>
       <c r="P3" t="n">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="Q3" t="n">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="R3" t="n">
-        <v>25902</v>
+        <v>25938</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5201044</v>
+        <v>4.520996</v>
       </c>
       <c r="G3" t="n">
-        <v>30161</v>
+        <v>30164</v>
       </c>
       <c r="H3" t="n">
-        <v>8884</v>
+        <v>8891</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2337395</v>
+        <v>2337424</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>May 7, 2026</t>
+          <t>May 19, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3132</v>
+        <v>3126</v>
       </c>
       <c r="O3" t="n">
         <v>279</v>
       </c>
       <c r="P3" t="n">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="R3" t="n">
-        <v>25938</v>
+        <v>25948</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35818</v>
+        <v>35930</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.520996</v>
+        <v>4.5171385</v>
       </c>
       <c r="G3" t="n">
-        <v>30164</v>
+        <v>30176</v>
       </c>
       <c r="H3" t="n">
-        <v>8891</v>
+        <v>8892</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2337424</v>
+        <v>2338145</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -649,23 +649,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>May 19, 2026</t>
+          <t>May 20, 2026</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3126</v>
+        <v>3147</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="R3" t="n">
-        <v>25948</v>
+        <v>25925</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46163</v>
+        <v>46164.48803318028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46163</v>
+        <v>46164.48803606692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5171385</v>
+        <v>4.5182157</v>
       </c>
       <c r="G3" t="n">
-        <v>30176</v>
+        <v>30185</v>
       </c>
       <c r="H3" t="n">
-        <v>8892</v>
+        <v>8896</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,947 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3147</v>
+        <v>3141</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="R3" t="n">
-        <v>25925</v>
+        <v>25942</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>46164.48803864543</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>com.arabbank.arabimobilev2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Arabi-Mobile</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Mobile App Conduct your banking transactions securely and on the go!</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3.6261437</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24829</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5567</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1,000,000+</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>2542893</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.21.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Jul 2, 2018</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>May 9, 2026</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>7155</v>
+      </c>
+      <c r="O4" t="n">
+        <v>842</v>
+      </c>
+      <c r="P4" t="n">
+        <v>891</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1167</v>
+      </c>
+      <c r="R4" t="n">
+        <v>14766</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>46164.48804108771</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>com.hbtf</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Iskan Mobile</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Housing Bank Mobile Application</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>4.5508256</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25637</v>
+      </c>
+      <c r="H5" t="n">
+        <v>9550</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>500,000+</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>645108</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>380.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Apr 19, 2020</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1859</v>
+      </c>
+      <c r="O5" t="n">
+        <v>288</v>
+      </c>
+      <c r="P5" t="n">
+        <v>756</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1692</v>
+      </c>
+      <c r="R5" t="n">
+        <v>21037</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46164.48804357093</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>com.icsfs.ajib.test</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AJIB Mobile</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Arab Jordan Investment Bank Mobile Banking</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="G6" t="n">
+        <v>440</v>
+      </c>
+      <c r="H6" t="n">
+        <v>158</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50,000+</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>90787</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Varies with device</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mar 13, 2017</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>139</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>17</v>
+      </c>
+      <c r="R6" t="n">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>46164.48804601603</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>com.ubanquity.ahli_jo</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ahli Mobile: Banking App</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Effortlessly Manage Your Accounts, Loans, Cards, And Transfers - Ahli Mobile</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4.8245616</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3071</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1147</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>414805</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>5.0.9</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sep 14, 2012</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Apr 2, 2026</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>107</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>39</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2895</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46164.48804857698</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>com.bankofjordan.mobileapp</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BOJ Mobile</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>BOJ MOBILE is the Mobile Banking service from Bank of Jordan.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>4.1958957</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5987</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2223</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>427083</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2.1.24</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Aug 21, 2018</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>May 6, 2026</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>948</v>
+      </c>
+      <c r="O8" t="n">
+        <v>144</v>
+      </c>
+      <c r="P8" t="n">
+        <v>178</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>222</v>
+      </c>
+      <c r="R8" t="n">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>46164.48805101532</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>com.mob.jkb</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>JKBMobile</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>More than just a Banking Application! The all-new JKB mobile application</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>4.0186915</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1210</v>
+      </c>
+      <c r="H9" t="n">
+        <v>491</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>173778</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1.7.15GMS</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Jul 21, 2022</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Apr 26, 2026</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>237</v>
+      </c>
+      <c r="O9" t="n">
+        <v>22</v>
+      </c>
+      <c r="P9" t="n">
+        <v>79</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>46164.48805343789</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>com.icsfs.mobile.rajhi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AlRajhi JO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Welcome to our new mobile app! We're excited to introduce new experience</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="G10" t="n">
+        <v>527</v>
+      </c>
+      <c r="H10" t="n">
+        <v>222</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50,000+</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>84613</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.8.7</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>May 5, 2024</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>May 9, 2026</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>125</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46164.48805597309</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>com.capital.cbt</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Capital Bank Mobile – Jordan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Capital Bank’s advanced mobile application covers all your daily banking needs</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>4.690513</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14456</v>
+      </c>
+      <c r="H11" t="n">
+        <v>689</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>248104</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.0.44</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Jun 20, 2022</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>May 4, 2026</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>696</v>
+      </c>
+      <c r="O11" t="n">
+        <v>156</v>
+      </c>
+      <c r="P11" t="n">
+        <v>247</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>718</v>
+      </c>
+      <c r="R11" t="n">
+        <v>12634</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>46164.48805861753</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>com.a2a.android.cab</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CAB Mobile Banking</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cairo Amman Bank customers can manage &amp; monitor their accounts securely.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2.5894737</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4632</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1913</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>346173</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Varies with device</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Jan 18, 2015</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>2559</v>
+      </c>
+      <c r="O12" t="n">
+        <v>133</v>
+      </c>
+      <c r="P12" t="n">
+        <v>158</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>206</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>46164.48806101629</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>com.blombank.eblom.jo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>eBLOM Jordan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>eBLOM Android App</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2.795699</v>
+      </c>
+      <c r="G13" t="n">
+        <v>111</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10,000+</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>21619</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>1.0.1.13</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>May 9, 2017</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Feb 25, 2026</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>53</v>
+      </c>
+      <c r="O13" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>46164.48806351746</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>com.fact.jib</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Jordan Islamic Bank</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Secure application provides JIB customers flexibility to perform transactions.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3.3981652</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11902</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4642</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1,000,000+</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1205306</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10.6.4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Jul 24, 2017</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Mar 27, 2026</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>4214</v>
+      </c>
+      <c r="O14" t="n">
+        <v>305</v>
+      </c>
+      <c r="P14" t="n">
+        <v>436</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>414</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6528</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>46164.48806604035</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>com.icsfs.safwa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Safwa Islamic Bank</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Conduct your banking transactions conveniently!</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3.3558824</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3854</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1554</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100,000+</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>384021</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>May 17, 2017</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Mar 15, 2026</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1427</v>
+      </c>
+      <c r="O15" t="n">
+        <v>113</v>
+      </c>
+      <c r="P15" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>101</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2118</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Google Play Store</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>46164.48807016087</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>com.iiab.mobilebanking</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Arabi Islami Mobile</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Islamic international Arab Bank (Arabi Islami Mobile)</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>4.7312307</v>
+      </c>
+      <c r="G16" t="n">
+        <v>46459</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2916</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>500,000+</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>544583</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2.0.2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Nov 11, 2021</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Jan 21, 2026</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>1924</v>
+      </c>
+      <c r="O16" t="n">
+        <v>338</v>
+      </c>
+      <c r="P16" t="n">
+        <v>709</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2350</v>
+      </c>
+      <c r="R16" t="n">
+        <v>41133</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -16,10 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -58,12 +55,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,8 +526,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>46164.48803318028</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:17</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -602,8 +600,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>46164.48803606692</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:17</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -674,8 +674,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>46164.48803864543</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:17</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -746,8 +748,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>46164.48804108771</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:18</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -818,8 +822,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>46164.48804357093</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:18</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -886,8 +892,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>46164.48804601603</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:18</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -958,8 +966,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>46164.48804857698</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:18</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1030,8 +1040,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>46164.48805101532</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:18</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1102,8 +1114,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>46164.48805343789</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:19</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1174,8 +1188,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>46164.48805597309</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:19</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1246,8 +1262,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>46164.48805861753</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:19</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1314,8 +1332,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>46164.48806101629</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:19</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1386,8 +1406,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>46164.48806351746</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:19</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1458,8 +1480,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>46164.48806604035</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:20</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1530,8 +1554,10 @@
           <t>Google Play Store</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>46164.48807016087</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-05-22 11:56:20</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:17</t>
+          <t>2026-05-22 12:42:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:17</t>
+          <t>2026-05-22 12:42:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:17</t>
+          <t>2026-05-22 12:42:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:18</t>
+          <t>2026-05-22 12:42:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5508256</v>
+        <v>4.5492835</v>
       </c>
       <c r="G5" t="n">
-        <v>25637</v>
+        <v>25638</v>
       </c>
       <c r="H5" t="n">
         <v>9550</v>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1859</v>
+        <v>1869</v>
       </c>
       <c r="O5" t="n">
         <v>288</v>
@@ -810,10 +810,10 @@
         <v>756</v>
       </c>
       <c r="Q5" t="n">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="R5" t="n">
-        <v>21037</v>
+        <v>21028</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:18</t>
+          <t>2026-05-22 12:42:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:18</t>
+          <t>2026-05-22 12:42:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:18</t>
+          <t>2026-05-22 12:42:11</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1958957</v>
+        <v>4.187384</v>
       </c>
       <c r="G8" t="n">
-        <v>5987</v>
+        <v>5990</v>
       </c>
       <c r="H8" t="n">
         <v>2223</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="O8" t="n">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="P8" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q8" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R8" t="n">
-        <v>4490</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:18</t>
+          <t>2026-05-22 12:42:11</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:19</t>
+          <t>2026-05-22 12:42:11</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:19</t>
+          <t>2026-05-22 12:42:11</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:19</t>
+          <t>2026-05-22 12:42:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:19</t>
+          <t>2026-05-22 12:42:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:19</t>
+          <t>2026-05-22 12:42:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3981652</v>
+        <v>3.3996334</v>
       </c>
       <c r="G14" t="n">
-        <v>11902</v>
+        <v>11903</v>
       </c>
       <c r="H14" t="n">
         <v>4642</v>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4214</v>
+        <v>4210</v>
       </c>
       <c r="O14" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P14" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q14" t="n">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R14" t="n">
-        <v>6528</v>
+        <v>6534</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:20</t>
+          <t>2026-05-22 12:42:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 11:56:20</t>
+          <t>2026-05-22 12:42:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7312307</v>
+        <v>4.73161</v>
       </c>
       <c r="G16" t="n">
-        <v>46459</v>
+        <v>46465</v>
       </c>
       <c r="H16" t="n">
         <v>2916</v>
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="O16" t="n">
         <v>338</v>
@@ -1616,10 +1616,10 @@
         <v>709</v>
       </c>
       <c r="Q16" t="n">
-        <v>2350</v>
+        <v>2346</v>
       </c>
       <c r="R16" t="n">
-        <v>41133</v>
+        <v>41146</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:09</t>
+          <t>2026-05-22 17:41:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:10</t>
+          <t>2026-05-22 17:41:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5182157</v>
+        <v>4.5183945</v>
       </c>
       <c r="G3" t="n">
-        <v>30185</v>
+        <v>30186</v>
       </c>
       <c r="H3" t="n">
-        <v>8896</v>
+        <v>8897</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3141</v>
+        <v>3140</v>
       </c>
       <c r="O3" t="n">
         <v>290</v>
@@ -665,7 +665,7 @@
         <v>515</v>
       </c>
       <c r="R3" t="n">
-        <v>25942</v>
+        <v>25945</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:10</t>
+          <t>2026-05-22 17:41:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:10</t>
+          <t>2026-05-22 17:41:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5492835</v>
+        <v>4.541084</v>
       </c>
       <c r="G5" t="n">
-        <v>25638</v>
+        <v>25643</v>
       </c>
       <c r="H5" t="n">
         <v>9550</v>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>645108</v>
+        <v>645385</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1869</v>
+        <v>1927</v>
       </c>
       <c r="O5" t="n">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>756</v>
+        <v>762</v>
       </c>
       <c r="Q5" t="n">
         <v>1691</v>
       </c>
       <c r="R5" t="n">
-        <v>21028</v>
+        <v>20979</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:10</t>
+          <t>2026-05-22 17:41:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,10 +846,10 @@
         <v>3.56</v>
       </c>
       <c r="G6" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H6" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:10</t>
+          <t>2026-05-22 17:41:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:11</t>
+          <t>2026-05-22 17:41:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.187384</v>
+        <v>4.188889</v>
       </c>
       <c r="G8" t="n">
-        <v>5990</v>
+        <v>5991</v>
       </c>
       <c r="H8" t="n">
         <v>2223</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="O8" t="n">
         <v>154</v>
@@ -1031,7 +1031,7 @@
         <v>221</v>
       </c>
       <c r="R8" t="n">
-        <v>4477</v>
+        <v>4482</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:11</t>
+          <t>2026-05-22 17:41:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:11</t>
+          <t>2026-05-22 17:41:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="H10" t="n">
         <v>222</v>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:11</t>
+          <t>2026-05-22 17:41:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1212,7 +1212,7 @@
         <v>4.690513</v>
       </c>
       <c r="G11" t="n">
-        <v>14456</v>
+        <v>14457</v>
       </c>
       <c r="H11" t="n">
         <v>689</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248104</v>
+        <v>248161</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>718</v>
       </c>
       <c r="R11" t="n">
-        <v>12634</v>
+        <v>12635</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:11</t>
+          <t>2026-05-22 17:41:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:12</t>
+          <t>2026-05-22 17:41:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:12</t>
+          <t>2026-05-22 17:41:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3996334</v>
+        <v>3.3945205</v>
       </c>
       <c r="G14" t="n">
-        <v>11903</v>
+        <v>11907</v>
       </c>
       <c r="H14" t="n">
         <v>4642</v>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4210</v>
+        <v>4229</v>
       </c>
       <c r="O14" t="n">
         <v>304</v>
       </c>
       <c r="P14" t="n">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q14" t="n">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R14" t="n">
-        <v>6534</v>
+        <v>6524</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:12</t>
+          <t>2026-05-22 17:41:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 12:42:12</t>
+          <t>2026-05-22 17:41:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.73161</v>
+        <v>4.7317414</v>
       </c>
       <c r="G16" t="n">
-        <v>46465</v>
+        <v>46482</v>
       </c>
       <c r="H16" t="n">
-        <v>2916</v>
+        <v>2917</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1920</v>
+        <v>1914</v>
       </c>
       <c r="O16" t="n">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="P16" t="n">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="Q16" t="n">
-        <v>2346</v>
+        <v>2350</v>
       </c>
       <c r="R16" t="n">
-        <v>41146</v>
+        <v>41161</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:53</t>
+          <t>2026-05-22 18:26:52</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:53</t>
+          <t>2026-05-22 18:26:52</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:54</t>
+          <t>2026-05-22 18:26:52</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:54</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.541084</v>
+        <v>4.541048</v>
       </c>
       <c r="G5" t="n">
-        <v>25643</v>
+        <v>25645</v>
       </c>
       <c r="H5" t="n">
         <v>9550</v>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="Q5" t="n">
-        <v>1691</v>
+        <v>1701</v>
       </c>
       <c r="R5" t="n">
-        <v>20979</v>
+        <v>20975</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:54</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:54</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:54</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.188889</v>
+        <v>4.190388</v>
       </c>
       <c r="G8" t="n">
         <v>5991</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="O8" t="n">
         <v>154</v>
       </c>
       <c r="P8" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="n">
         <v>221</v>
       </c>
       <c r="R8" t="n">
-        <v>4482</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:55</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:55</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:55</t>
+          <t>2026-05-22 18:26:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:55</t>
+          <t>2026-05-22 18:26:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>346173</v>
+        <v>346261</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:55</t>
+          <t>2026-05-22 18:26:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:56</t>
+          <t>2026-05-22 18:26:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1433,7 +1433,7 @@
         <v>11907</v>
       </c>
       <c r="H14" t="n">
-        <v>4642</v>
+        <v>4643</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:56</t>
+          <t>2026-05-22 18:26:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 17:41:56</t>
+          <t>2026-05-22 18:26:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7317414</v>
+        <v>4.7318673</v>
       </c>
       <c r="G16" t="n">
-        <v>46482</v>
+        <v>46485</v>
       </c>
       <c r="H16" t="n">
         <v>2917</v>
@@ -1610,16 +1610,16 @@
         <v>1914</v>
       </c>
       <c r="O16" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P16" t="n">
         <v>706</v>
       </c>
       <c r="Q16" t="n">
-        <v>2350</v>
+        <v>2349</v>
       </c>
       <c r="R16" t="n">
-        <v>41161</v>
+        <v>41166</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:52</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:52</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:52</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -775,7 +775,7 @@
         <v>25645</v>
       </c>
       <c r="H5" t="n">
-        <v>9550</v>
+        <v>9551</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>90787</v>
+        <v>91055</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -990,7 +990,7 @@
         <v>4.190388</v>
       </c>
       <c r="G8" t="n">
-        <v>5991</v>
+        <v>5992</v>
       </c>
       <c r="H8" t="n">
         <v>2223</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="O8" t="n">
         <v>154</v>
@@ -1031,7 +1031,7 @@
         <v>221</v>
       </c>
       <c r="R8" t="n">
-        <v>4484</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:53</t>
+          <t>2026-05-22 18:51:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:54</t>
+          <t>2026-05-22 18:51:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:54</t>
+          <t>2026-05-22 18:51:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:54</t>
+          <t>2026-05-22 18:51:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1205306</v>
+        <v>1205791</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:54</t>
+          <t>2026-05-22 18:51:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>384021</v>
+        <v>384184</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 18:26:54</t>
+          <t>2026-05-22 18:51:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
         <v>4.009901</v>
       </c>
       <c r="G2" t="n">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H2" t="n">
         <v>153</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35930</v>
+        <v>35956</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5183945</v>
+        <v>4.5165367</v>
       </c>
       <c r="G3" t="n">
-        <v>30186</v>
+        <v>30198</v>
       </c>
       <c r="H3" t="n">
-        <v>8897</v>
+        <v>8896</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2338145</v>
+        <v>2338688</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3140</v>
+        <v>3152</v>
       </c>
       <c r="O3" t="n">
         <v>290</v>
@@ -662,10 +662,10 @@
         <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="R3" t="n">
-        <v>25945</v>
+        <v>25933</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6261437</v>
+        <v>3.6252453</v>
       </c>
       <c r="G4" t="n">
-        <v>24829</v>
+        <v>24831</v>
       </c>
       <c r="H4" t="n">
         <v>5567</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2542893</v>
+        <v>2543786</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7155</v>
+        <v>7160</v>
       </c>
       <c r="O4" t="n">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14766</v>
+        <v>14760</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.541048</v>
+        <v>4.5398345</v>
       </c>
       <c r="G5" t="n">
-        <v>25645</v>
+        <v>25653</v>
       </c>
       <c r="H5" t="n">
-        <v>9551</v>
+        <v>9555</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1925</v>
+        <v>1931</v>
       </c>
       <c r="O5" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P5" t="n">
-        <v>760</v>
+        <v>769</v>
       </c>
       <c r="Q5" t="n">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="R5" t="n">
-        <v>20975</v>
+        <v>20972</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H6" t="n">
         <v>159</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="R6" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:26</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>414805</v>
+        <v>415076</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:27</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,13 +987,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.190388</v>
+        <v>4.188192</v>
       </c>
       <c r="G8" t="n">
-        <v>5992</v>
+        <v>5993</v>
       </c>
       <c r="H8" t="n">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>427083</v>
+        <v>427127</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="O8" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P8" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="Q8" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="R8" t="n">
-        <v>4485</v>
+        <v>4477</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:27</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>173778</v>
+        <v>173835</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:27</t>
+          <t>2026-05-23 17:51:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:27</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.690513</v>
+        <v>4.6936235</v>
       </c>
       <c r="G11" t="n">
-        <v>14457</v>
+        <v>14465</v>
       </c>
       <c r="H11" t="n">
         <v>689</v>
@@ -1247,13 +1247,13 @@
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>247</v>
+        <v>224</v>
       </c>
       <c r="Q11" t="n">
         <v>718</v>
       </c>
       <c r="R11" t="n">
-        <v>12635</v>
+        <v>12664</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:27</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1289,7 +1289,7 @@
         <v>4632</v>
       </c>
       <c r="H12" t="n">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:28</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:28</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3945205</v>
+        <v>3.396536</v>
       </c>
       <c r="G14" t="n">
-        <v>11907</v>
+        <v>11910</v>
       </c>
       <c r="H14" t="n">
-        <v>4643</v>
+        <v>4645</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,16 +1459,16 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4229</v>
+        <v>4222</v>
       </c>
       <c r="O14" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="P14" t="n">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q14" t="n">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="R14" t="n">
         <v>6524</v>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:28</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3558824</v>
+        <v>3.3607037</v>
       </c>
       <c r="G15" t="n">
-        <v>3854</v>
+        <v>3855</v>
       </c>
       <c r="H15" t="n">
         <v>1554</v>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1427</v>
+        <v>1424</v>
       </c>
       <c r="O15" t="n">
         <v>113</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2118</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-22 18:51:28</t>
+          <t>2026-05-23 17:51:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7318673</v>
+        <v>4.7325745</v>
       </c>
       <c r="G16" t="n">
-        <v>46485</v>
+        <v>46519</v>
       </c>
       <c r="H16" t="n">
         <v>2917</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="O16" t="n">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P16" t="n">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="Q16" t="n">
-        <v>2349</v>
+        <v>2344</v>
       </c>
       <c r="R16" t="n">
-        <v>41166</v>
+        <v>41211</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:22</t>
+          <t>2026-05-24 17:48:25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:22</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5165367</v>
+        <v>4.5189734</v>
       </c>
       <c r="G3" t="n">
-        <v>30198</v>
+        <v>30203</v>
       </c>
       <c r="H3" t="n">
-        <v>8896</v>
+        <v>8908</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2338688</v>
+        <v>2340465</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3152</v>
+        <v>3134</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="R3" t="n">
-        <v>25933</v>
+        <v>25955</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6252453</v>
+        <v>3.627041</v>
       </c>
       <c r="G4" t="n">
         <v>24831</v>
       </c>
       <c r="H4" t="n">
-        <v>5567</v>
+        <v>5568</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2543786</v>
+        <v>2545823</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7160</v>
+        <v>7151</v>
       </c>
       <c r="O4" t="n">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="R4" t="n">
-        <v>14760</v>
+        <v>14774</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5398345</v>
+        <v>4.5354333</v>
       </c>
       <c r="G5" t="n">
-        <v>25653</v>
+        <v>25665</v>
       </c>
       <c r="H5" t="n">
-        <v>9555</v>
+        <v>9559</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1931</v>
+        <v>1952</v>
       </c>
       <c r="O5" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P5" t="n">
-        <v>769</v>
+        <v>785</v>
       </c>
       <c r="Q5" t="n">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="R5" t="n">
-        <v>20972</v>
+        <v>20949</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H6" t="n">
         <v>159</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O6" t="n">
         <v>7</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>415076</v>
+        <v>415967</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.0.9</t>
+          <t>5.1.0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Apr 2, 2026</t>
+          <t>May 23, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:26</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.188192</v>
+        <v>4.172608</v>
       </c>
       <c r="G8" t="n">
-        <v>5993</v>
+        <v>5994</v>
       </c>
       <c r="H8" t="n">
         <v>2224</v>
@@ -1001,11 +1001,11 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>427127</v>
+        <v>427615</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2.1.24</t>
+          <t>2.1.25</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1015,23 +1015,23 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>May 6, 2026</t>
+          <t>May 20, 2026</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>949</v>
+        <v>977</v>
       </c>
       <c r="O8" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="Q8" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="R8" t="n">
-        <v>4477</v>
+        <v>4452</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:23</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6936235</v>
+        <v>4.6913486</v>
       </c>
       <c r="G11" t="n">
-        <v>14465</v>
+        <v>14468</v>
       </c>
       <c r="H11" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12664</v>
+        <v>12652</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5894737</v>
+        <v>2.5853019</v>
       </c>
       <c r="G12" t="n">
-        <v>4632</v>
+        <v>4633</v>
       </c>
       <c r="H12" t="n">
         <v>1914</v>
@@ -1311,19 +1311,19 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2559</v>
+        <v>2565</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
       </c>
       <c r="P12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R12" t="n">
-        <v>1571</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="13">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.396536</v>
+        <v>3.390554</v>
       </c>
       <c r="G14" t="n">
-        <v>11910</v>
+        <v>11913</v>
       </c>
       <c r="H14" t="n">
-        <v>4645</v>
+        <v>4648</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4222</v>
+        <v>4230</v>
       </c>
       <c r="O14" t="n">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="P14" t="n">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="Q14" t="n">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="R14" t="n">
-        <v>6524</v>
+        <v>6502</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-23 17:51:24</t>
+          <t>2026-05-24 17:48:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7325745</v>
+        <v>4.732456</v>
       </c>
       <c r="G16" t="n">
-        <v>46519</v>
+        <v>46549</v>
       </c>
       <c r="H16" t="n">
-        <v>2917</v>
+        <v>2919</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>544583</v>
+        <v>545883</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.0.2</t>
+          <t>3.1.0</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1603,23 +1603,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Jan 21, 2026</t>
+          <t>May 21, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1912</v>
+        <v>1923</v>
       </c>
       <c r="O16" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="P16" t="n">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="Q16" t="n">
-        <v>2344</v>
+        <v>2331</v>
       </c>
       <c r="R16" t="n">
-        <v>41211</v>
+        <v>41251</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:25</t>
+          <t>2026-05-25 15:37:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.009901</v>
+        <v>4.029126</v>
       </c>
       <c r="G2" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H2" t="n">
         <v>153</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>35956</v>
+        <v>36159</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5189734</v>
+        <v>4.5165367</v>
       </c>
       <c r="G3" t="n">
-        <v>30203</v>
+        <v>30219</v>
       </c>
       <c r="H3" t="n">
-        <v>8908</v>
+        <v>8912</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2340465</v>
+        <v>2341710</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3134</v>
+        <v>3154</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="R3" t="n">
-        <v>25955</v>
+        <v>25951</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.627041</v>
+        <v>3.620013</v>
       </c>
       <c r="G4" t="n">
-        <v>24831</v>
+        <v>24836</v>
       </c>
       <c r="H4" t="n">
-        <v>5568</v>
+        <v>5569</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2545823</v>
+        <v>2546362</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7151</v>
+        <v>7195</v>
       </c>
       <c r="O4" t="n">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="Q4" t="n">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="R4" t="n">
-        <v>14774</v>
+        <v>14732</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5354333</v>
+        <v>4.535839</v>
       </c>
       <c r="G5" t="n">
-        <v>25665</v>
+        <v>25680</v>
       </c>
       <c r="H5" t="n">
-        <v>9559</v>
+        <v>9561</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>645385</v>
+        <v>646412</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1952</v>
+        <v>1963</v>
       </c>
       <c r="O5" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>785</v>
+        <v>762</v>
       </c>
       <c r="Q5" t="n">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>20949</v>
+        <v>20976</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>91055</v>
+        <v>91929</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>3071</v>
       </c>
       <c r="H7" t="n">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>415967</v>
+        <v>416209</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:26</t>
+          <t>2026-05-25 15:37:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.172608</v>
+        <v>4.1779027</v>
       </c>
       <c r="G8" t="n">
-        <v>5994</v>
+        <v>5996</v>
       </c>
       <c r="H8" t="n">
         <v>2224</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>427615</v>
+        <v>427837</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="O8" t="n">
         <v>145</v>
       </c>
       <c r="P8" t="n">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="Q8" t="n">
         <v>224</v>
       </c>
       <c r="R8" t="n">
-        <v>4452</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>173835</v>
+        <v>174107</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H10" t="n">
         <v>222</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>84613</v>
+        <v>84946</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6913486</v>
+        <v>4.6884737</v>
       </c>
       <c r="G11" t="n">
-        <v>14468</v>
+        <v>14479</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248161</v>
+        <v>248514</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1253,7 +1253,7 @@
         <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12652</v>
+        <v>12651</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>346261</v>
+        <v>346826</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21619</v>
+        <v>21631</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.390554</v>
+        <v>3.4123616</v>
       </c>
       <c r="G14" t="n">
-        <v>11913</v>
+        <v>11920</v>
       </c>
       <c r="H14" t="n">
         <v>4648</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1205791</v>
+        <v>1208880</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4230</v>
+        <v>4167</v>
       </c>
       <c r="O14" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="P14" t="n">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="Q14" t="n">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="R14" t="n">
-        <v>6502</v>
+        <v>6563</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:27</t>
+          <t>2026-05-25 15:37:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,10 +1504,10 @@
         <v>3.3607037</v>
       </c>
       <c r="G15" t="n">
-        <v>3855</v>
+        <v>3856</v>
       </c>
       <c r="H15" t="n">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>384184</v>
+        <v>384816</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-24 17:48:28</t>
+          <t>2026-05-25 15:37:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.732456</v>
+        <v>4.731975</v>
       </c>
       <c r="G16" t="n">
-        <v>46549</v>
+        <v>46585</v>
       </c>
       <c r="H16" t="n">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,11 +1589,11 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>545883</v>
+        <v>546248</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.1.1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1603,23 +1603,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>May 21, 2026</t>
+          <t>May 25, 2026</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1923</v>
+        <v>1939</v>
       </c>
       <c r="O16" t="n">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P16" t="n">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="Q16" t="n">
-        <v>2331</v>
+        <v>2313</v>
       </c>
       <c r="R16" t="n">
-        <v>41251</v>
+        <v>41295</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:00</t>
+          <t>2026-05-25 18:20:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:00</t>
+          <t>2026-05-25 18:20:46</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:00</t>
+          <t>2026-05-25 18:20:46</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.620013</v>
+        <v>3.620915</v>
       </c>
       <c r="G4" t="n">
-        <v>24836</v>
+        <v>24838</v>
       </c>
       <c r="H4" t="n">
         <v>5569</v>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7195</v>
+        <v>7190</v>
       </c>
       <c r="O4" t="n">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="P4" t="n">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="Q4" t="n">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="R4" t="n">
-        <v>14732</v>
+        <v>14739</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:00</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:00</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:01</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:01</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:01</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:01</t>
+          <t>2026-05-25 18:20:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:01</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6884737</v>
+        <v>4.688716</v>
       </c>
       <c r="G11" t="n">
-        <v>14479</v>
+        <v>14480</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1253,7 +1253,7 @@
         <v>721</v>
       </c>
       <c r="R11" t="n">
-        <v>12651</v>
+        <v>12654</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:02</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:02</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:02</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4123616</v>
+        <v>3.4101381</v>
       </c>
       <c r="G14" t="n">
-        <v>11920</v>
+        <v>11921</v>
       </c>
       <c r="H14" t="n">
-        <v>4648</v>
+        <v>4649</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4167</v>
+        <v>4174</v>
       </c>
       <c r="O14" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P14" t="n">
         <v>449</v>
@@ -1471,7 +1471,7 @@
         <v>427</v>
       </c>
       <c r="R14" t="n">
-        <v>6563</v>
+        <v>6558</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:02</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-25 15:37:02</t>
+          <t>2026-05-25 18:20:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.731975</v>
+        <v>4.7319303</v>
       </c>
       <c r="G16" t="n">
-        <v>46585</v>
+        <v>46590</v>
       </c>
       <c r="H16" t="n">
         <v>2920</v>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1939</v>
+        <v>1938</v>
       </c>
       <c r="O16" t="n">
         <v>340</v>
       </c>
       <c r="P16" t="n">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="Q16" t="n">
-        <v>2313</v>
+        <v>2322</v>
       </c>
       <c r="R16" t="n">
-        <v>41295</v>
+        <v>41293</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:46</t>
+          <t>2026-05-26 19:12:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -553,7 +553,7 @@
         <v>360</v>
       </c>
       <c r="H2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:46</t>
+          <t>2026-05-26 19:12:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5165367</v>
+        <v>4.513383</v>
       </c>
       <c r="G3" t="n">
-        <v>30219</v>
+        <v>30229</v>
       </c>
       <c r="H3" t="n">
-        <v>8912</v>
+        <v>8915</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3154</v>
+        <v>3179</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P3" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q3" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="R3" t="n">
-        <v>25951</v>
+        <v>25935</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:46</t>
+          <t>2026-05-26 19:12:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.620915</v>
       </c>
       <c r="G4" t="n">
-        <v>24838</v>
+        <v>24841</v>
       </c>
       <c r="H4" t="n">
         <v>5569</v>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7190</v>
+        <v>7191</v>
       </c>
       <c r="O4" t="n">
         <v>842</v>
@@ -739,7 +739,7 @@
         <v>1167</v>
       </c>
       <c r="R4" t="n">
-        <v>14739</v>
+        <v>14741</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.535839</v>
+        <v>4.535076</v>
       </c>
       <c r="G5" t="n">
-        <v>25680</v>
+        <v>25687</v>
       </c>
       <c r="H5" t="n">
-        <v>9561</v>
+        <v>9564</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="Q5" t="n">
-        <v>1693</v>
+        <v>1700</v>
       </c>
       <c r="R5" t="n">
-        <v>20976</v>
+        <v>20974</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>4.8245616</v>
       </c>
       <c r="G7" t="n">
-        <v>3071</v>
+        <v>3072</v>
       </c>
       <c r="H7" t="n">
         <v>1148</v>
@@ -957,7 +957,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>2895</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>5996</v>
       </c>
       <c r="H8" t="n">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:47</t>
+          <t>2026-05-26 19:12:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.688716</v>
+        <v>4.6892</v>
       </c>
       <c r="G11" t="n">
-        <v>14480</v>
+        <v>14485</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>235</v>
       </c>
       <c r="Q11" t="n">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="R11" t="n">
-        <v>12654</v>
+        <v>12660</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:11</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:11</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4101381</v>
+        <v>3.4190564</v>
       </c>
       <c r="G14" t="n">
-        <v>11921</v>
+        <v>11925</v>
       </c>
       <c r="H14" t="n">
-        <v>4649</v>
+        <v>4652</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4174</v>
+        <v>4147</v>
       </c>
       <c r="O14" t="n">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P14" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Q14" t="n">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="R14" t="n">
-        <v>6558</v>
+        <v>6585</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,13 +1501,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3607037</v>
+        <v>3.3450294</v>
       </c>
       <c r="G15" t="n">
-        <v>3856</v>
+        <v>3858</v>
       </c>
       <c r="H15" t="n">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1424</v>
+        <v>1432</v>
       </c>
       <c r="O15" t="n">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R15" t="n">
-        <v>2125</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-25 18:20:48</t>
+          <t>2026-05-26 19:12:11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7319303</v>
+        <v>4.729569</v>
       </c>
       <c r="G16" t="n">
-        <v>46590</v>
+        <v>46604</v>
       </c>
       <c r="H16" t="n">
-        <v>2920</v>
+        <v>2922</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1938</v>
+        <v>1987</v>
       </c>
       <c r="O16" t="n">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="P16" t="n">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="Q16" t="n">
-        <v>2322</v>
+        <v>2286</v>
       </c>
       <c r="R16" t="n">
-        <v>41293</v>
+        <v>41306</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:09</t>
+          <t>2026-05-27 19:11:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.029126</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H2" t="n">
         <v>154</v>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36159</v>
+        <v>36205</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O2" t="n">
         <v>6</v>
@@ -591,7 +591,7 @@
         <v>13</v>
       </c>
       <c r="R2" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:09</t>
+          <t>2026-05-27 19:11:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.513383</v>
+        <v>4.5122495</v>
       </c>
       <c r="G3" t="n">
-        <v>30229</v>
+        <v>30233</v>
       </c>
       <c r="H3" t="n">
-        <v>8915</v>
+        <v>8921</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2341710</v>
+        <v>2342521</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3179</v>
+        <v>3186</v>
       </c>
       <c r="O3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P3" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="R3" t="n">
-        <v>25935</v>
+        <v>25922</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:09</t>
+          <t>2026-05-27 19:11:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -698,7 +698,7 @@
         <v>3.620915</v>
       </c>
       <c r="G4" t="n">
-        <v>24841</v>
+        <v>24842</v>
       </c>
       <c r="H4" t="n">
         <v>5569</v>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2546362</v>
+        <v>2547134</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:09</t>
+          <t>2026-05-27 19:11:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.535076</v>
+        <v>4.5307994</v>
       </c>
       <c r="G5" t="n">
-        <v>25687</v>
+        <v>25692</v>
       </c>
       <c r="H5" t="n">
-        <v>9564</v>
+        <v>9565</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>646412</v>
+        <v>646680</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1968</v>
+        <v>1996</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="Q5" t="n">
-        <v>1700</v>
+        <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>20974</v>
+        <v>20955</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:09</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="H6" t="n">
         <v>159</v>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>91929</v>
+        <v>92277</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="R6" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:10</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8245616</v>
+        <v>4.826087</v>
       </c>
       <c r="G7" t="n">
-        <v>3072</v>
+        <v>3074</v>
       </c>
       <c r="H7" t="n">
         <v>1148</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>416209</v>
+        <v>416855</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>2896</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:10</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.1779027</v>
+        <v>4.17757</v>
       </c>
       <c r="G8" t="n">
-        <v>5996</v>
+        <v>5997</v>
       </c>
       <c r="H8" t="n">
         <v>2225</v>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="O8" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P8" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q8" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4468</v>
+        <v>4461</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:10</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,7 +1064,7 @@
         <v>4.0186915</v>
       </c>
       <c r="G9" t="n">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="H9" t="n">
         <v>491</v>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174107</v>
+        <v>174193</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 26, 2026</t>
+          <t>Apr 25, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:10</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,10 +1138,10 @@
         <v>3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H10" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>84946</v>
+        <v>85143</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:10</t>
+          <t>2026-05-27 19:11:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6892</v>
+        <v>4.6901627</v>
       </c>
       <c r="G11" t="n">
-        <v>14485</v>
+        <v>14489</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248514</v>
+        <v>248516</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q11" t="n">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="R11" t="n">
-        <v>12660</v>
+        <v>12670</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:11</t>
+          <t>2026-05-27 19:11:49</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>346826</v>
+        <v>346956</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:11</t>
+          <t>2026-05-27 19:11:49</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21631</v>
+        <v>21644</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:11</t>
+          <t>2026-05-27 19:11:49</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4190564</v>
+        <v>3.4160516</v>
       </c>
       <c r="G14" t="n">
-        <v>11925</v>
+        <v>11929</v>
       </c>
       <c r="H14" t="n">
         <v>4652</v>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1208880</v>
+        <v>1209790</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4147</v>
+        <v>4159</v>
       </c>
       <c r="O14" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P14" t="n">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q14" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R14" t="n">
-        <v>6585</v>
+        <v>6579</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:11</t>
+          <t>2026-05-27 19:11:49</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1507,7 +1507,7 @@
         <v>3858</v>
       </c>
       <c r="H15" t="n">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>384816</v>
+        <v>385269</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 15, 2026</t>
+          <t>Mar 14, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-26 19:12:11</t>
+          <t>2026-05-27 19:11:49</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,13 +1575,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.729569</v>
+        <v>4.728181</v>
       </c>
       <c r="G16" t="n">
-        <v>46604</v>
+        <v>46616</v>
       </c>
       <c r="H16" t="n">
-        <v>2922</v>
+        <v>2923</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>546248</v>
+        <v>546724</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1987</v>
+        <v>2006</v>
       </c>
       <c r="O16" t="n">
         <v>321</v>
       </c>
       <c r="P16" t="n">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="Q16" t="n">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="R16" t="n">
-        <v>41306</v>
+        <v>41305</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:47</t>
+          <t>2026-05-28 19:32:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36205</v>
+        <v>36292</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:47</t>
+          <t>2026-05-28 19:32:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5122495</v>
+        <v>4.509266</v>
       </c>
       <c r="G3" t="n">
-        <v>30233</v>
+        <v>30242</v>
       </c>
       <c r="H3" t="n">
-        <v>8921</v>
+        <v>8926</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,11 +635,11 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2342521</v>
+        <v>2342959</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.41.1</t>
+          <t>4.42.1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -653,19 +653,19 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3186</v>
+        <v>3216</v>
       </c>
       <c r="O3" t="n">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="P3" t="n">
         <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>538</v>
+        <v>548</v>
       </c>
       <c r="R3" t="n">
-        <v>25922</v>
+        <v>25903</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:47</t>
+          <t>2026-05-28 19:32:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.620915</v>
+        <v>3.6236138</v>
       </c>
       <c r="G4" t="n">
-        <v>24842</v>
+        <v>24844</v>
       </c>
       <c r="H4" t="n">
-        <v>5569</v>
+        <v>5570</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2547134</v>
+        <v>2548795</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7191</v>
+        <v>7179</v>
       </c>
       <c r="O4" t="n">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P4" t="n">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="Q4" t="n">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="R4" t="n">
-        <v>14741</v>
+        <v>14762</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:47</t>
+          <t>2026-05-28 19:32:14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5307994</v>
+        <v>4.5310044</v>
       </c>
       <c r="G5" t="n">
-        <v>25692</v>
+        <v>25693</v>
       </c>
       <c r="H5" t="n">
-        <v>9565</v>
+        <v>9567</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>646680</v>
+        <v>647046</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>20955</v>
+        <v>20957</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>92277</v>
+        <v>92798</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -919,7 +919,7 @@
         <v>3074</v>
       </c>
       <c r="H7" t="n">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>5997</v>
       </c>
       <c r="H8" t="n">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>427837</v>
+        <v>428038</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174193</v>
+        <v>174328</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1138,7 +1138,7 @@
         <v>3.87</v>
       </c>
       <c r="G10" t="n">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H10" t="n">
         <v>224</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85143</v>
+        <v>85227</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O10" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>25</v>
       </c>
       <c r="R10" t="n">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:48</t>
+          <t>2026-05-28 19:32:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6901627</v>
+        <v>4.690642</v>
       </c>
       <c r="G11" t="n">
-        <v>14489</v>
+        <v>14490</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248516</v>
+        <v>248629</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O11" t="n">
         <v>156</v>
@@ -1250,10 +1250,10 @@
         <v>234</v>
       </c>
       <c r="Q11" t="n">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="R11" t="n">
-        <v>12670</v>
+        <v>12673</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:49</t>
+          <t>2026-05-28 19:32:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>346956</v>
+        <v>346991</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:49</t>
+          <t>2026-05-28 19:32:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21644</v>
+        <v>21648</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:49</t>
+          <t>2026-05-28 19:32:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4160516</v>
+        <v>3.4205174</v>
       </c>
       <c r="G14" t="n">
-        <v>11929</v>
+        <v>11932</v>
       </c>
       <c r="H14" t="n">
-        <v>4652</v>
+        <v>4653</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1209790</v>
+        <v>1210194</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4159</v>
+        <v>4145</v>
       </c>
       <c r="O14" t="n">
         <v>307</v>
@@ -1471,7 +1471,7 @@
         <v>429</v>
       </c>
       <c r="R14" t="n">
-        <v>6579</v>
+        <v>6594</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:49</t>
+          <t>2026-05-28 19:32:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3450294</v>
+        <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3858</v>
+        <v>3859</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>385269</v>
+        <v>385357</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1432</v>
+        <v>1448</v>
       </c>
       <c r="O15" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2108</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-27 19:11:49</t>
+          <t>2026-05-28 19:32:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.728181</v>
+        <v>4.7273374</v>
       </c>
       <c r="G16" t="n">
-        <v>46616</v>
+        <v>46625</v>
       </c>
       <c r="H16" t="n">
         <v>2923</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>546724</v>
+        <v>546956</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1607,19 +1607,19 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="O16" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P16" t="n">
-        <v>697</v>
+        <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2283</v>
+        <v>2301</v>
       </c>
       <c r="R16" t="n">
-        <v>41305</v>
+        <v>41280</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:13</t>
+          <t>2026-05-29 19:25:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:13</t>
+          <t>2026-05-29 19:25:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.509266</v>
+        <v>4.508902</v>
       </c>
       <c r="G3" t="n">
-        <v>30242</v>
+        <v>30253</v>
       </c>
       <c r="H3" t="n">
         <v>8926</v>
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3216</v>
+        <v>3219</v>
       </c>
       <c r="O3" t="n">
         <v>279</v>
@@ -662,10 +662,10 @@
         <v>290</v>
       </c>
       <c r="Q3" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="R3" t="n">
-        <v>25903</v>
+        <v>25909</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:13</t>
+          <t>2026-05-29 19:25:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.6236138</v>
+        <v>3.624511</v>
       </c>
       <c r="G4" t="n">
-        <v>24844</v>
+        <v>24846</v>
       </c>
       <c r="H4" t="n">
-        <v>5570</v>
+        <v>5571</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2548795</v>
+        <v>2548796</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7179</v>
+        <v>7174</v>
       </c>
       <c r="O4" t="n">
         <v>841</v>
@@ -739,7 +739,7 @@
         <v>1165</v>
       </c>
       <c r="R4" t="n">
-        <v>14762</v>
+        <v>14771</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:14</t>
+          <t>2026-05-29 19:25:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5310044</v>
+        <v>4.5333624</v>
       </c>
       <c r="G5" t="n">
-        <v>25693</v>
+        <v>25696</v>
       </c>
       <c r="H5" t="n">
-        <v>9567</v>
+        <v>9568</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647046</v>
+        <v>647177</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
       </c>
       <c r="P5" t="n">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="Q5" t="n">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="R5" t="n">
-        <v>20957</v>
+        <v>20977</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:14</t>
+          <t>2026-05-29 19:25:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -846,7 +846,7 @@
         <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H6" t="n">
         <v>159</v>
@@ -883,7 +883,7 @@
         <v>17</v>
       </c>
       <c r="R6" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7">
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:14</t>
+          <t>2026-05-29 19:25:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.826087</v>
+        <v>4.8103447</v>
       </c>
       <c r="G7" t="n">
-        <v>3074</v>
+        <v>3076</v>
       </c>
       <c r="H7" t="n">
         <v>1149</v>
@@ -927,7 +927,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>416855</v>
+        <v>417140</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="O7" t="n">
         <v>12</v>
@@ -957,7 +957,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>2899</v>
+        <v>2889</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:14</t>
+          <t>2026-05-29 19:25:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4.17757</v>
+        <v>4.1700935</v>
       </c>
       <c r="G8" t="n">
-        <v>5997</v>
+        <v>5999</v>
       </c>
       <c r="H8" t="n">
         <v>2227</v>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428038</v>
+        <v>428095</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>974</v>
+        <v>986</v>
       </c>
       <c r="O8" t="n">
         <v>144</v>
@@ -1031,7 +1031,7 @@
         <v>234</v>
       </c>
       <c r="R8" t="n">
-        <v>4461</v>
+        <v>4450</v>
       </c>
     </row>
     <row r="9">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:14</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Apr 25, 2026</t>
+          <t>Apr 26, 2026</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:15</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:15</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.690642</v>
+        <v>4.691596</v>
       </c>
       <c r="G11" t="n">
-        <v>14490</v>
+        <v>14496</v>
       </c>
       <c r="H11" t="n">
         <v>690</v>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248629</v>
+        <v>248682</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="O11" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P11" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="Q11" t="n">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="R11" t="n">
-        <v>12673</v>
+        <v>12684</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:15</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:15</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:15</t>
+          <t>2026-05-29 19:25:38</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4205174</v>
+        <v>3.4271219</v>
       </c>
       <c r="G14" t="n">
-        <v>11932</v>
+        <v>11934</v>
       </c>
       <c r="H14" t="n">
         <v>4653</v>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4145</v>
+        <v>4127</v>
       </c>
       <c r="O14" t="n">
         <v>307</v>
@@ -1471,7 +1471,7 @@
         <v>429</v>
       </c>
       <c r="R14" t="n">
-        <v>6594</v>
+        <v>6616</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:16</t>
+          <t>2026-05-29 19:25:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>385357</v>
+        <v>385358</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mar 14, 2026</t>
+          <t>Mar 15, 2026</t>
         </is>
       </c>
       <c r="N15" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-28 19:32:16</t>
+          <t>2026-05-29 19:25:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1578,7 +1578,7 @@
         <v>4.7273374</v>
       </c>
       <c r="G16" t="n">
-        <v>46625</v>
+        <v>46624</v>
       </c>
       <c r="H16" t="n">
         <v>2923</v>
@@ -1619,7 +1619,7 @@
         <v>2301</v>
       </c>
       <c r="R16" t="n">
-        <v>41280</v>
+        <v>41279</v>
       </c>
     </row>
   </sheetData>

--- a/data/Jordan_banks_Reviews_GooglePlay.xlsx
+++ b/data/Jordan_banks_Reviews_GooglePlay.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:36</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>36292</v>
+        <v>36337</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:36</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.508902</v>
+        <v>4.509469</v>
       </c>
       <c r="G3" t="n">
-        <v>30253</v>
+        <v>30249</v>
       </c>
       <c r="H3" t="n">
-        <v>8926</v>
+        <v>8927</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2342959</v>
+        <v>2344161</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3219</v>
+        <v>3222</v>
       </c>
       <c r="O3" t="n">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P3" t="n">
         <v>290</v>
@@ -665,7 +665,7 @@
         <v>549</v>
       </c>
       <c r="R3" t="n">
-        <v>25909</v>
+        <v>25912</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:36</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.624511</v>
+        <v>3.6241043</v>
       </c>
       <c r="G4" t="n">
-        <v>24846</v>
+        <v>24843</v>
       </c>
       <c r="H4" t="n">
-        <v>5571</v>
+        <v>5570</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2548796</v>
+        <v>2550034</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -727,19 +727,19 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>7174</v>
+        <v>7184</v>
       </c>
       <c r="O4" t="n">
         <v>841</v>
       </c>
       <c r="P4" t="n">
-        <v>889</v>
+        <v>873</v>
       </c>
       <c r="Q4" t="n">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="R4" t="n">
-        <v>14771</v>
+        <v>14775</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:37</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.5333624</v>
+        <v>4.5310044</v>
       </c>
       <c r="G5" t="n">
-        <v>25696</v>
+        <v>25690</v>
       </c>
       <c r="H5" t="n">
-        <v>9568</v>
+        <v>9570</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>647177</v>
+        <v>647517</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>1983</v>
+        <v>1996</v>
       </c>
       <c r="O5" t="n">
         <v>279</v>
@@ -810,10 +810,10 @@
         <v>761</v>
       </c>
       <c r="Q5" t="n">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="R5" t="n">
-        <v>20977</v>
+        <v>20955</v>
       </c>
     </row>
     <row r="6">
@@ -824,7 +824,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:37</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>92798</v>
+        <v>93410</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:37</t>
+          <t>2026-05-30 17:54:50</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -913,13 +913,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8103447</v>
+        <v>4.8111587</v>
       </c>
       <c r="G7" t="n">
-        <v>3076</v>
+        <v>3077</v>
       </c>
       <c r="H7" t="n">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>417140</v>
+        <v>417681</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.1.0</t>
+          <t>5.1.1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>May 23, 2026</t>
+          <t>May 27, 2026</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -957,7 +957,7 @@
         <v>39</v>
       </c>
       <c r="R7" t="n">
-        <v>2889</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="8">
@@ -968,7 +968,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:37</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -993,7 +993,7 @@
         <v>5999</v>
       </c>
       <c r="H8" t="n">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>428095</v>
+        <v>428316</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1064,10 +1064,10 @@
         <v>4.0186915</v>
       </c>
       <c r="G9" t="n">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="H9" t="n">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>174328</v>
+        <v>174428</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>85227</v>
+        <v>85366</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.691596</v>
+        <v>4.6876945</v>
       </c>
       <c r="G11" t="n">
-        <v>14496</v>
+        <v>14498</v>
       </c>
       <c r="H11" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>248682</v>
+        <v>248807</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>703</v>
+        <v>722</v>
       </c>
       <c r="O11" t="n">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="P11" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Q11" t="n">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="R11" t="n">
-        <v>12684</v>
+        <v>12668</v>
       </c>
     </row>
     <row r="12">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1286,7 +1286,7 @@
         <v>2.5853019</v>
       </c>
       <c r="G12" t="n">
-        <v>4633</v>
+        <v>4634</v>
       </c>
       <c r="H12" t="n">
         <v>1914</v>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>346991</v>
+        <v>347136</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="O12" t="n">
         <v>133</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:51</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1367,7 +1367,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>21648</v>
+        <v>21659</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:38</t>
+          <t>2026-05-30 17:54:52</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4271219</v>
+        <v>3.4195933</v>
       </c>
       <c r="G14" t="n">
-        <v>11934</v>
+        <v>11939</v>
       </c>
       <c r="H14" t="n">
-        <v>4653</v>
+        <v>4656</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1210194</v>
+        <v>1211174</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4127</v>
+        <v>4159</v>
       </c>
       <c r="O14" t="n">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P14" t="n">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="Q14" t="n">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="R14" t="n">
-        <v>6616</v>
+        <v>6608</v>
       </c>
     </row>
     <row r="15">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:39</t>
+          <t>2026-05-30 17:54:52</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1504,7 +1504,7 @@
         <v>3.3284457</v>
       </c>
       <c r="G15" t="n">
-        <v>3859</v>
+        <v>3857</v>
       </c>
       <c r="H15" t="n">
         <v>1557</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>385358</v>
+        <v>385618</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="O15" t="n">
         <v>124</v>
@@ -1545,7 +1545,7 @@
         <v>101</v>
       </c>
       <c r="R15" t="n">
-        <v>2092</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="16">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-05-29 19:25:39</t>
+          <t>2026-05-30 17:54:52</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.7273374</v>
+        <v>4.727402</v>
       </c>
       <c r="G16" t="n">
-        <v>46624</v>
+        <v>46621</v>
       </c>
       <c r="H16" t="n">
         <v>2923</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>546956</v>
+        <v>547440</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         <v>718</v>
       </c>
       <c r="Q16" t="n">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="R16" t="n">
-        <v>41279</v>
+        <v>41278</v>
       </c>
     </row>
   </sheetData>
